--- a/coachgrid/Vereine_Schweiz.xlsx
+++ b/coachgrid/Vereine_Schweiz.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -702,66 +702,66 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Spalte «Link geprüft»</t>
+          <t>Kontrollwerte Stand 28.07.2026 (die Formeln oben müssen dasselbe ergeben)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Link ok – Website wurde am 28.07.2026 angesteuert und hat geantwortet (HTTP 200/301).</t>
+          <t>Golf: 103 Einträge, 92 mit Telefon, 71 mit E-Mail, 94 Websites ok</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Prüfen – Server blockt automatische Aufrufe (403/406) oder antwortete nicht rechtzeitig; im Browser meist normal erreichbar.</t>
+          <t>Tennis: 99 Einträge, 33 mit Telefon, 21 mit E-Mail, 79 Websites ok</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Link tot – Adresse liefert 404 oder einen Serverfehler.</t>
+          <t>Schwimmen: 180 Einträge, 0 mit Telefon, 0 mit E-Mail, 157 Websites ok</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Reiten &amp; Eishockey: 32 Einträge, 29 mit Telefon, 12 mit E-Mail, 19 Websites ok</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Was diese Liste NICHT ist</t>
-        </is>
-      </c>
+      <c r="A17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Telefonnummern und Mailadressen stammen 1:1 aus der Quelle und wurden nicht nachtelefoniert.</t>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Spalte «Link geprüft»</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>OpenStreetMap ist nicht vollständig: Vereine ohne eigene Anlage fehlen dort häufig ganz.</t>
+          <t>Link ok – Website wurde am 28.07.2026 angesteuert und hat geantwortet (HTTP 200/301).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Bei Schwimmen publiziert Swiss Aquatics keine Telefonnummern – dort gibt es Website und Ort.</t>
+          <t>Prüfen – Server blockt automatische Aufrufe (403/406) oder antwortete nicht rechtzeitig; im Browser meist normal erreichbar.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Für eine lückenlose Liste pro Sportart braucht es die Verbandsverzeichnisse (Swiss Tennis, Swiss Golf, football.ch, stv-fsg.ch, sihf.ch).</t>
+          <t>Link tot – Adresse liefert 404 oder einen Serverfehler.</t>
         </is>
       </c>
     </row>
@@ -769,14 +769,52 @@
       <c r="A22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Die Spalte «Priorität» kommt aus der Marktanalyse (coachgrid/marktanalyse-vereine.md):</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Was diese Liste NICHT ist</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Telefonnummern und Mailadressen stammen 1:1 aus der Quelle und wurden nicht nachtelefoniert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>OpenStreetMap ist nicht vollständig: Vereine ohne eigene Anlage fehlen dort häufig ganz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Bei Schwimmen publiziert Swiss Aquatics keine Telefonnummern – dort gibt es Website und Ort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Für eine lückenlose Liste pro Sportart braucht es die Verbandsverzeichnisse (Swiss Tennis, Swiss Golf, football.ch, stv-fsg.ch, sihf.ch).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Die Spalte «Priorität» kommt aus der Marktanalyse (coachgrid/marktanalyse-vereine.md):</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>A = eigene Anlage und angestelltes Personal, echtes Budget. B = eigene Anlage, kleines Budget.</t>
         </is>
